--- a/splists_out/needs_revision/plotsbci_not_garwood.xlsx
+++ b/splists_out/needs_revision/plotsbci_not_garwood.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,167 +447,147 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>forestgeo_current_name</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>orig_infraspecies_rank</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sp6prior</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>IDLevel</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_name</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_authors</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_rank</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_status</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_plant_name_id</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_matched_ipni_id</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>match_similarity</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_plant_name_id</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_powo_id</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_ipni_id</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_binomial</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_name</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_authority</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_family</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_genus</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_species</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_infrarank</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_infraspecies</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_rank</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_lifeform</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>origmatches</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>names_notes</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>wcvp_accepted_duplicated</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>sp4</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>orig_name</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>orig_infraspecies_rank</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sp6prior</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>IDLevel</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_name</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_authors</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_rank</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_status</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_plant_name_id</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_matched_ipni_id</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>match_similarity</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_plant_name_id</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_powo_id</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_ipni_id</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_binomial</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_name</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_authority</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_family</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_genus</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_species</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_infrarank</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_infraspecies</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_rank</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>wcvp_accepted_lifeform</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>origmatches</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>names_notes</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>current_name</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>current_authority</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>current_family</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>current_genus</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>current_species</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>current_binomial</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>sp4</t>
         </is>
       </c>
     </row>
@@ -787,6 +767,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Jupunba idiopoda</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -964,9 +954,19 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>CUP2</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
         </is>
       </c>
     </row>
@@ -1146,9 +1146,19 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
         <is>
           <t>MYRF</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
     </row>
@@ -1328,9 +1338,19 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>NEC2</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
         </is>
       </c>
     </row>
@@ -1510,9 +1530,19 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
         <is>
           <t>UNO2</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
         </is>
       </c>
     </row>

--- a/splists_out/needs_revision/plotsbci_not_garwood.xlsx
+++ b/splists_out/needs_revision/plotsbci_not_garwood.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -594,27 +594,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abarid</t>
+          <t>tachve</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>bcimultiplots</t>
+          <t>bci50ha, bcimultiplots, bci10ha, P14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -629,22 +634,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jupunba</t>
+          <t>Tachigali</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>idiopoda</t>
+          <t>panamensis</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>(S.F. Blake) M.V.B. Soares, M.P. Morim &amp; Iganci</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Pithecellobium pseudotamarindus, Abarema idiopoda</t>
+          <t>van der Werff &amp; N. Zamora</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>abarid</t>
+          <t>tachve</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>(S.F.Blake) M.V.B.Soares, M.P.Morim &amp; Iganci</t>
+          <t>van der Werff &amp; N.Zamora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3274630</t>
+          <t>2899124</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>77218789-1</t>
+          <t>77108226-1</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -709,32 +709,32 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3274630</t>
+          <t>2899124</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>77218789-1</t>
+          <t>77108226-1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>77218789-1</t>
+          <t>77108226-1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>(S.F.Blake) M.V.B.Soares, M.P.Morim &amp; Iganci</t>
+          <t>van der Werff &amp; N.Zamora</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Jupunba</t>
+          <t>Tachigali</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>idiopoda</t>
+          <t>panamensis</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -757,11 +757,6 @@
           <t>Species</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>tree</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -772,66 +767,71 @@
           <t>FALSE</t>
         </is>
       </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>TACV</t>
+        </is>
+      </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Jupunba idiopoda</t>
+          <t>Tachigali panamensis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cupasc</t>
+          <t>abarid</t>
         </is>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>bci50ha</t>
+          <t>bcimultiplots</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sapindales</t>
+          <t>Fabales</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Cupania</t>
+          <t>Jupunba</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>scrobiculata</t>
+          <t>idiopoda</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Rich.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>R. Pérez 2474 (PMA, SCZ)</t>
+          <t>(S.F. Blake) M.V.B. Soares, M.P. Morim &amp; Iganci</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Pithecellobium pseudotamarindus, Abarema idiopoda</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>cupasc</t>
+          <t>abarid</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Rich.</t>
+          <t>(S.F.Blake) M.V.B.Soares, M.P.Morim &amp; Iganci</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2747671</t>
+          <t>3274630</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>782556-1</t>
+          <t>77218789-1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2747671</t>
+          <t>3274630</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>782556-1</t>
+          <t>77218789-1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>782556-1</t>
+          <t>77218789-1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Rich.</t>
+          <t>(S.F.Blake) M.V.B.Soares, M.P.Morim &amp; Iganci</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Cupania</t>
+          <t>Jupunba</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>scrobiculata</t>
+          <t>idiopoda</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>shrub or tree</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -959,28 +959,28 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>CUP2</t>
-        </is>
-      </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Cupania scrobiculata</t>
+          <t>Jupunba idiopoda</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>myr2fl</t>
+          <t>ardife</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ardisia fendleri</t>
         </is>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -993,37 +993,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>bcimultiplots</t>
+          <t>bci50ha, bcimultiplots, bci10ha</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Myrtales</t>
+          <t>Ericales</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Primulaceae</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Myrciaria</t>
+          <t>Ardisia</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>floribunda</t>
+          <t>copeyana</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>(H. West ex Willd.) O. Berg</t>
+          <t>Standl.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>R. Pérez 2347 (PMA, SCZ)</t>
+          <t>R. Pérez 1974 (PMA, SCZ)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>myr2fl</t>
+          <t>ardife</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>(H.West ex Willd.) O.Berg</t>
+          <t>Standl.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>2647760</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>18102-2</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1088,47 +1088,47 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>2647760</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>18102-2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>18102-2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>(H.West ex Willd.) O.Berg</t>
+          <t>Standl.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Primulaceae</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Myrciaria</t>
+          <t>Ardisia</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>floribunda</t>
+          <t>copeyana</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>shrub or tree</t>
+          <t>shrub</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1153,23 +1153,28 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>MYRF</t>
+          <t>ARDF</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ardisia copeyana</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nectcu</t>
+          <t>cestme</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1181,41 +1186,46 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>bcimultiplots</t>
+          <t>bci50ha</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Laurales</t>
+          <t>Solanales</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nectandra</t>
+          <t>Cestrum</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>cuspidata</t>
+          <t>schlechtendalii</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Nees &amp; Mart.</t>
+          <t>G. Don</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Nectandra gentlei</t>
+          <t>Cestrum megalophyllum</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>R. Pérez 1886 (PMA, SCZ)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1225,17 +1235,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>nectcu</t>
+          <t>cestme</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1245,12 +1255,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Nees &amp; Mart.</t>
+          <t>G.Don</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1265,12 +1275,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2379054</t>
+          <t>2713787</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>281229-2</t>
+          <t>330712-2</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1280,47 +1290,47 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2379054</t>
+          <t>2713787</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>281229-2</t>
+          <t>330712-2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>281229-2</t>
+          <t>330712-2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Nees &amp; Mart.</t>
+          <t>G.Don</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Nectandra</t>
+          <t>Cestrum</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>cuspidata</t>
+          <t>schlechtendalii</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1330,7 +1340,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>shrub</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1345,204 +1355,2563 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>NEC2</t>
+          <t>CES2</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Nectandra cuspidata</t>
+          <t>Cestrum schlechtendalii</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>cupasc</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bci50ha</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sapindales</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Cupania</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>scrobiculata</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Rich.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>R. Pérez 2474 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>cupasc</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Rich.</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2747671</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>782556-1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2747671</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>782556-1</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>782556-1</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rich.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Cupania</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>CUP2</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Cupania scrobiculata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ficubu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bcimultiplots</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Rosales</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ficus</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>matiziana</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Dugand</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Ficus bullenei</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>R. Pérez 1117 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ficubu</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Dugand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2811277</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>104625-2</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2811277</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>104625-2</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>104625-2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Dugand</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Ficus</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>matiziana</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>FIBU</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Ficus matiziana</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>myr2fl</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bcimultiplots</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Myrtales</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Myrciaria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>floribunda</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>(H. West ex Willd.) O. Berg</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>R. Pérez 2347 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>myr2fl</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>(H.West ex Willd.) O.Berg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>131815</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>599327-1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>131815</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>599327-1</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>599327-1</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>(H.West ex Willd.) O.Berg</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Myrciaria</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>floribunda</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>MYRF</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>myrcze</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bcimultiplots</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Myrtales</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Myrcia</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tomentosa</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>(Aubl.) DC.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Aulomyrcia tomentosa, Aulomyrcia zetekiana</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>myrcze</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>(Aubl.) DC.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>131684</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>599215-1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>131684</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>599215-1</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>599215-1</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>(Aubl.) DC.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Myrcia</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>tomentosa</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>MYRZ</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Myrcia tomentosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>nectcu</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bcimultiplots</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Laurales</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Nectandra</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>cuspidata</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Nees &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Nectandra gentlei</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>nectcu</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Nees &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2379054</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>281229-2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2379054</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>281229-2</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>281229-2</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Nees &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Nectandra</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>cuspidata</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>NEC2</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Nectandra cuspidata</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>nectpu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Damburneya umbrosa</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>86</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>14</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, bci10ha, P14, P11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Laurales</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Damburneya</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>purpurea</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>(Ruiz &amp; Pav.) Trofimov</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Nectandra purpurea</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>R. Pérez 1872 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>nectpu</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>(Ruiz &amp; Pav.) Trofimov</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3009192</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>77158867-1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>3009192</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>77158867-1</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>77158867-1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>(Ruiz &amp; Pav.) Trofimov</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Damburneya</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>purpurea</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>NECP</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Damburneya purpurea</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pipecu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Piper culebranum</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bci50ha, P11</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Piperales</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Piperaceae</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Piper</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>colonense</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>C. DC.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>pipecu</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C.DC.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2557497</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2557497</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>C.DC.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Piperaceae</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Piper</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>colonense</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>PPCU</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pla1pi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Platymiscium pinnatum</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>158</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, bci10ha</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Fabales</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Platymiscium</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>dimorphandrum</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Donn. Sm.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Platymiscium pinnatum</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>R. Pérez 2149 y 2186 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>pla1pi</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Donn.Sm.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2539397</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>515221-1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2539397</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>515221-1</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>515221-1</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Donn.Sm.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Platymiscium</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>dimorphandrum</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>PLAP</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Platymiscium dimorphandrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quaras</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quararibea asterolepis</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>2417</v>
+      </c>
+      <c r="D14">
+        <v>73</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>243</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, bci10ha, P14, P11</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Malvales</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Quararibea</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>stenophylla</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>R. Pérez 2042 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>quaras</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2868400</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2868400</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Quararibea</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>stenophylla</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>QUA1</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>stemgr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana grandiflora</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, P14</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Gentianales</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Apocynaceae</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>africana</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Stemmadenia grandiflora, Tabernaemontana grandiflora</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>R. Pérez 1850 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>stemgr</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>200551</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>77177359-1</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>200551</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>77177359-1</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>77177359-1</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Apocynaceae</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>africana</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>STEG</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Tabernaemontana africana</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tremin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Trema integerrima</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, P14</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Rosales</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Cannabaceae</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Trema</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>domingense</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Urb.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Trema integerrimum</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>R. Pérez 2293 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>tremin</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Urb.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2518702</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>256535-2</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2518702</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>256535-2</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>256535-2</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Urb.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Cannabaceae</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Trema</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>domingense</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Trema domingense</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>unonpa</t>
         </is>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>bcimultiplots</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Magnoliales</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Unonopsis</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>panamensis</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>R.E. Fr.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>R. Pérez 2303 (PMA, SCZ)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Freestanding</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>unonpa</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>R.E.Fr.</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2447472</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>259517-2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2447472</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>259517-2</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>259517-2</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>R.E.Fr.</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>Unonopsis</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>panamensis</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>tree</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>UNO2</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>virosp</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Virola multiflora</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bci50ha, bcimultiplots, bci10ha</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Magnoliales</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Myristicaceae</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>fosteri</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>D. Santam.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>R. Pérez 1130 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>virosp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D.Santam.</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3237737</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>77202547-1</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>3237737</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>77202547-1</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>77202547-1</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>D.Santam.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Myristicaceae</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>fosteri</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>VIR3</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Virola fosteri</t>
         </is>
       </c>
     </row>
